--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_365_R37.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_365_R37.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.6609</v>
+        <v>9.1258</v>
       </c>
       <c r="E2" t="n">
-        <v>7.3783</v>
+        <v>8.4398</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2826</v>
+        <v>0.6859</v>
       </c>
       <c r="G2" t="n">
         <v>5.8584</v>
@@ -610,13 +610,13 @@
         <v>0.9278</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.7336</v>
+        <v>0.7312</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.8215</v>
+        <v>0.2401</v>
       </c>
       <c r="U2" t="n">
-        <v>0.08790000000000001</v>
+        <v>0.4911</v>
       </c>
       <c r="V2" t="n">
         <v>1.6083</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>N. REUVERS</t>
+          <t>B. BADIO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.0268</v>
+        <v>4.0914</v>
       </c>
       <c r="E3" t="n">
-        <v>5.8056</v>
+        <v>4.6751</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.7788</v>
+        <v>-0.5837</v>
       </c>
       <c r="G3" t="n">
-        <v>3.7649</v>
+        <v>4.5502</v>
       </c>
       <c r="H3" t="n">
-        <v>2.1187</v>
+        <v>-1.2616</v>
       </c>
       <c r="I3" t="n">
-        <v>1.6462</v>
+        <v>5.8118</v>
       </c>
       <c r="J3" t="n">
-        <v>4.8303</v>
+        <v>4.0537</v>
       </c>
       <c r="K3" t="n">
-        <v>2.7091</v>
+        <v>-1.1323</v>
       </c>
       <c r="L3" t="n">
-        <v>2.1212</v>
+        <v>5.186</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.0655</v>
+        <v>0.4964</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.5904</v>
+        <v>-0.1294</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.4751</v>
+        <v>0.6258</v>
       </c>
       <c r="P3" t="n">
-        <v>0.4639</v>
+        <v>0.232</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-0.232</v>
       </c>
       <c r="R3" t="n">
         <v>0.4639</v>
       </c>
       <c r="S3" t="n">
-        <v>2.012</v>
+        <v>1.0594</v>
       </c>
       <c r="T3" t="n">
-        <v>0.9752</v>
+        <v>0.8532999999999999</v>
       </c>
       <c r="U3" t="n">
-        <v>1.0368</v>
+        <v>0.206</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.214</v>
+        <v>-1.7501</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.214</v>
+        <v>-1.7501</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>B. BADIO</t>
+          <t>N. REUVERS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.4344</v>
+        <v>4.0173</v>
       </c>
       <c r="E4" t="n">
-        <v>4.0853</v>
+        <v>5.3338</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.6509</v>
+        <v>-1.3165</v>
       </c>
       <c r="G4" t="n">
-        <v>4.5502</v>
+        <v>3.7649</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.2616</v>
+        <v>2.1187</v>
       </c>
       <c r="I4" t="n">
-        <v>5.8118</v>
+        <v>1.6462</v>
       </c>
       <c r="J4" t="n">
-        <v>4.0537</v>
+        <v>4.8303</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.1323</v>
+        <v>2.7091</v>
       </c>
       <c r="L4" t="n">
-        <v>5.186</v>
+        <v>2.1212</v>
       </c>
       <c r="M4" t="n">
-        <v>0.4964</v>
+        <v>-1.0655</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.1294</v>
+        <v>-0.5904</v>
       </c>
       <c r="O4" t="n">
-        <v>0.6258</v>
+        <v>-0.4751</v>
       </c>
       <c r="P4" t="n">
-        <v>0.232</v>
+        <v>0.4639</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.232</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
         <v>0.4639</v>
       </c>
       <c r="S4" t="n">
-        <v>0.4024</v>
+        <v>1.0025</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2636</v>
+        <v>0.5034</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1388</v>
+        <v>0.4991</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.7501</v>
+        <v>-1.214</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.7501</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.3921</v>
+        <v>2.4758</v>
       </c>
       <c r="E5" t="n">
-        <v>3.5314</v>
+        <v>3.4135</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.1393</v>
+        <v>-0.9376</v>
       </c>
       <c r="G5" t="n">
         <v>1.5382</v>
@@ -844,13 +844,13 @@
         <v>1.1598</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0738</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1889</v>
+        <v>0.0709</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2627</v>
+        <v>-0.0611</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>N. SAKO</t>
+          <t>B. KEY</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.7147</v>
+        <v>1.2118</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6143</v>
+        <v>0.1498</v>
       </c>
       <c r="F6" t="n">
-        <v>1.1004</v>
+        <v>1.0619</v>
       </c>
       <c r="G6" t="n">
-        <v>1.0641</v>
+        <v>-1.8406</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.4417</v>
+        <v>-0.1776</v>
       </c>
       <c r="I6" t="n">
-        <v>1.5057</v>
+        <v>-1.663</v>
       </c>
       <c r="J6" t="n">
-        <v>0.5747</v>
+        <v>-1.2361</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.1982</v>
+        <v>0.4236</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7729</v>
+        <v>-1.6597</v>
       </c>
       <c r="M6" t="n">
-        <v>0.4893</v>
+        <v>-0.6044</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.2435</v>
+        <v>-0.6012</v>
       </c>
       <c r="O6" t="n">
-        <v>0.7328</v>
+        <v>-0.0033</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.1598</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1598</v>
+        <v>-1.3917</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>0.9278</v>
       </c>
       <c r="S6" t="n">
-        <v>1.8104</v>
+        <v>1.5136</v>
       </c>
       <c r="T6" t="n">
-        <v>1.1993</v>
+        <v>0.6332</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6111</v>
+        <v>0.8804</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>2.0026</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>2.1444</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.3876</v>
+        <v>1.1847</v>
       </c>
       <c r="E7" t="n">
-        <v>1.9619</v>
+        <v>1.4901</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.5742</v>
+        <v>-0.3054</v>
       </c>
       <c r="G7" t="n">
         <v>1.7153</v>
@@ -1000,13 +1000,13 @@
         <v>0.9278</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1362</v>
+        <v>-0.0668</v>
       </c>
       <c r="T7" t="n">
-        <v>0.7512</v>
+        <v>0.2794</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.615</v>
+        <v>-0.3462</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>B. KEY</t>
+          <t>N. SAKO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.3297</v>
+        <v>0.8389</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2678</v>
+        <v>-0.0934</v>
       </c>
       <c r="F8" t="n">
-        <v>1.0619</v>
+        <v>0.9324</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.8406</v>
+        <v>1.0641</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.1776</v>
+        <v>-0.4417</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.663</v>
+        <v>1.5057</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.2361</v>
+        <v>0.5747</v>
       </c>
       <c r="K8" t="n">
-        <v>0.4236</v>
+        <v>-0.1982</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.6597</v>
+        <v>0.7729</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.6044</v>
+        <v>0.4893</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.6012</v>
+        <v>-0.2435</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.0033</v>
+        <v>0.7328</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.4639</v>
+        <v>-1.1598</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.3917</v>
+        <v>-1.1598</v>
       </c>
       <c r="R8" t="n">
-        <v>0.9278</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>1.6316</v>
+        <v>0.9346</v>
       </c>
       <c r="T8" t="n">
-        <v>0.7512</v>
+        <v>0.4916</v>
       </c>
       <c r="U8" t="n">
-        <v>0.8804</v>
+        <v>0.443</v>
       </c>
       <c r="V8" t="n">
-        <v>2.0026</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>2.1444</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9409</v>
+        <v>0.8071</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.1076</v>
+        <v>-0.8717</v>
       </c>
       <c r="F9" t="n">
-        <v>2.0485</v>
+        <v>1.6788</v>
       </c>
       <c r="G9" t="n">
         <v>0.2244</v>
@@ -1156,13 +1156,13 @@
         <v>0.4639</v>
       </c>
       <c r="S9" t="n">
-        <v>1.6443</v>
+        <v>1.5105</v>
       </c>
       <c r="T9" t="n">
-        <v>0.3383</v>
+        <v>0.5742</v>
       </c>
       <c r="U9" t="n">
-        <v>1.306</v>
+        <v>0.9364</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>K. TAYLOR</t>
+          <t>J. PRADILLA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.146</v>
+        <v>-0.1839</v>
       </c>
       <c r="E10" t="n">
-        <v>0.2175</v>
+        <v>-0.4785</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.3635</v>
+        <v>0.2946</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.3339</v>
+        <v>0.4177</v>
       </c>
       <c r="H10" t="n">
-        <v>0.168</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.502</v>
+        <v>-0.2643</v>
       </c>
       <c r="J10" t="n">
-        <v>1.007</v>
+        <v>0.5396</v>
       </c>
       <c r="K10" t="n">
-        <v>1.4522</v>
+        <v>0.9579</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.4452</v>
+        <v>-0.4183</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.3409</v>
+        <v>-0.1219</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.2842</v>
+        <v>-0.2759</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.0568</v>
+        <v>0.154</v>
       </c>
       <c r="P10" t="n">
+        <v>-0.4639</v>
+      </c>
+      <c r="Q10" t="n">
         <v>-1.1598</v>
       </c>
-      <c r="Q10" t="n">
-        <v>-2.3195</v>
-      </c>
       <c r="R10" t="n">
-        <v>1.1598</v>
+        <v>0.6959</v>
       </c>
       <c r="S10" t="n">
-        <v>1.2059</v>
+        <v>-0.1377</v>
       </c>
       <c r="T10" t="n">
-        <v>1.3882</v>
+        <v>0.1417</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1823</v>
+        <v>-0.2794</v>
       </c>
       <c r="V10" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.4279</v>
+        <v>-0.5286999999999999</v>
       </c>
       <c r="E11" t="n">
         <v>-0.5764</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1485</v>
+        <v>0.0477</v>
       </c>
       <c r="G11" t="n">
         <v>-0.8167</v>
@@ -1312,13 +1312,13 @@
         <v>0.232</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1568</v>
+        <v>0.056</v>
       </c>
       <c r="T11" t="n">
         <v>-0.1494</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3062</v>
+        <v>0.2054</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. PRADILLA</t>
+          <t>K. TAYLOR</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,64 +1345,64 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.7736</v>
+        <v>-1.056</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.0683</v>
+        <v>-0.7261</v>
       </c>
       <c r="F12" t="n">
-        <v>0.2946</v>
+        <v>-0.3299</v>
       </c>
       <c r="G12" t="n">
-        <v>0.4177</v>
+        <v>-0.3339</v>
       </c>
       <c r="H12" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.168</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.2643</v>
+        <v>-0.502</v>
       </c>
       <c r="J12" t="n">
-        <v>0.5396</v>
+        <v>1.007</v>
       </c>
       <c r="K12" t="n">
-        <v>0.9579</v>
+        <v>1.4522</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.4183</v>
+        <v>-0.4452</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.1219</v>
+        <v>-1.3409</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.2759</v>
+        <v>-1.2842</v>
       </c>
       <c r="O12" t="n">
-        <v>0.154</v>
+        <v>-0.0568</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.4639</v>
+        <v>-1.1598</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.1598</v>
+        <v>-2.3195</v>
       </c>
       <c r="R12" t="n">
-        <v>0.6959</v>
+        <v>1.1598</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.7275</v>
+        <v>0.2959</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4481</v>
+        <v>0.4446</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2794</v>
+        <v>-0.1487</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="X12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.5762</v>
+        <v>-6.0207</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.9571</v>
+        <v>-3.6033</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.6191</v>
+        <v>-2.4174</v>
       </c>
       <c r="G13" t="n">
         <v>-1.4739</v>
@@ -1468,13 +1468,13 @@
         <v>0.6959</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.5456</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.5228</v>
+        <v>-0.1689</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0228</v>
+        <v>0.1788</v>
       </c>
       <c r="V13" t="n">
         <v>-2.933</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>15.9634</v>
+        <v>15.9635</v>
       </c>
       <c r="E14" t="n">
         <v>17.1527</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.189299999999999</v>
+        <v>-1.1892</v>
       </c>
       <c r="G14" t="n">
         <v>14.6681</v>
@@ -1531,13 +1531,13 @@
         <v>-5.311999999999999</v>
       </c>
       <c r="N14" t="n">
-        <v>-6.065900000000001</v>
+        <v>-6.0659</v>
       </c>
       <c r="O14" t="n">
         <v>0.7537000000000003</v>
       </c>
       <c r="P14" t="n">
-        <v>-3.479299999999999</v>
+        <v>-3.4793</v>
       </c>
       <c r="Q14" t="n">
         <v>-11.5977</v>
@@ -1546,13 +1546,13 @@
         <v>8.118499999999999</v>
       </c>
       <c r="S14" t="n">
-        <v>6.919100000000001</v>
+        <v>6.919</v>
       </c>
       <c r="T14" t="n">
-        <v>3.914099999999999</v>
+        <v>3.9141</v>
       </c>
       <c r="U14" t="n">
-        <v>3.005</v>
+        <v>3.0048</v>
       </c>
       <c r="V14" t="n">
         <v>-2.1444</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.2071</v>
+        <v>1.6618</v>
       </c>
       <c r="E15" t="n">
-        <v>2.0212</v>
+        <v>2.3751</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.8141</v>
+        <v>-0.7133</v>
       </c>
       <c r="G15" t="n">
         <v>-0.9634</v>
@@ -1624,13 +1624,13 @@
         <v>2.0876</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.5485</v>
+        <v>-1.0939</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.8487</v>
+        <v>-0.4949</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.6998</v>
+        <v>-0.599</v>
       </c>
       <c r="V15" t="n">
         <v>2.7912</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.038</v>
+        <v>0.4833</v>
       </c>
       <c r="E16" t="n">
-        <v>1.5892</v>
+        <v>1.7072</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.6272</v>
+        <v>-1.2239</v>
       </c>
       <c r="G16" t="n">
         <v>-0.7302999999999999</v>
@@ -1702,13 +1702,13 @@
         <v>1.8556</v>
       </c>
       <c r="S16" t="n">
-        <v>-2.0937</v>
+        <v>-1.5725</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6326000000000001</v>
+        <v>-0.5145999999999999</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.4611</v>
+        <v>-1.0578</v>
       </c>
       <c r="V16" t="n">
         <v>0.9304</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0876</v>
+        <v>-0.07049999999999999</v>
       </c>
       <c r="E17" t="n">
-        <v>1.2041</v>
+        <v>1.3221</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.2917</v>
+        <v>-1.3925</v>
       </c>
       <c r="G17" t="n">
         <v>-0.4764</v>
@@ -1780,13 +1780,13 @@
         <v>0.232</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1568</v>
+        <v>0.174</v>
       </c>
       <c r="T17" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.1259</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1489</v>
+        <v>0.0481</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.8376</v>
+        <v>-0.4337</v>
       </c>
       <c r="E19" t="n">
-        <v>1.3242</v>
+        <v>1.5601</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.1618</v>
+        <v>-1.9938</v>
       </c>
       <c r="G19" t="n">
         <v>0.3491</v>
@@ -1936,13 +1936,13 @@
         <v>1.3917</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.8826000000000001</v>
+        <v>-0.4786</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.7389</v>
+        <v>-0.503</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1436</v>
+        <v>0.0244</v>
       </c>
       <c r="V19" t="n">
         <v>-0.5361</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. HERNANGOMEZ</t>
+          <t>M. LESSORT</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.355</v>
+        <v>-1.8145</v>
       </c>
       <c r="E20" t="n">
-        <v>0.1413</v>
+        <v>0.7876</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.4963</v>
+        <v>-2.6021</v>
       </c>
       <c r="G20" t="n">
-        <v>-3.2041</v>
+        <v>-2.2841</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.1392</v>
+        <v>-1.3206</v>
       </c>
       <c r="I20" t="n">
-        <v>-3.0649</v>
+        <v>-0.9635</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.8735000000000001</v>
+        <v>0.0569</v>
       </c>
       <c r="K20" t="n">
-        <v>1.4487</v>
+        <v>-0.09039999999999999</v>
       </c>
       <c r="L20" t="n">
-        <v>-2.3222</v>
+        <v>0.1472</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.3305</v>
+        <v>-2.3409</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.5879</v>
+        <v>-1.2303</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.7426</v>
+        <v>-1.1107</v>
       </c>
       <c r="P20" t="n">
-        <v>1.1598</v>
+        <v>1.6237</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.1598</v>
+        <v>1.6237</v>
       </c>
       <c r="S20" t="n">
-        <v>0.6893</v>
+        <v>-0.7598</v>
       </c>
       <c r="T20" t="n">
-        <v>1.0148</v>
+        <v>-0.4832</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3255</v>
+        <v>-0.2765</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-0.3943</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.214</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. LESSORT</t>
+          <t>N. HAYES-DAVIS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.3776</v>
+        <v>-2.4238</v>
       </c>
       <c r="E21" t="n">
-        <v>0.7876</v>
+        <v>0.6032</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.1652</v>
+        <v>-3.027</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.2841</v>
+        <v>-1.4878</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.3206</v>
+        <v>-0.735</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.9635</v>
+        <v>-0.7528</v>
       </c>
       <c r="J21" t="n">
-        <v>0.0569</v>
+        <v>1.8328</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.09039999999999999</v>
+        <v>1.2106</v>
       </c>
       <c r="L21" t="n">
-        <v>0.1472</v>
+        <v>0.6222</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.3409</v>
+        <v>-3.3205</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.2303</v>
+        <v>-1.9456</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.1107</v>
+        <v>-1.375</v>
       </c>
       <c r="P21" t="n">
-        <v>1.6237</v>
+        <v>0.6959</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R21" t="n">
-        <v>1.6237</v>
+        <v>1.8556</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3229</v>
+        <v>-0.8431999999999999</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4832</v>
+        <v>-0.3534</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1604</v>
+        <v>-0.4898</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.3943</v>
+        <v>-0.7886</v>
       </c>
       <c r="W21" t="n">
-        <v>1.214</v>
+        <v>0.2836</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.6083</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>N. HAYES-DAVIS</t>
+          <t>J. HERNANGOMEZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.0357</v>
+        <v>-2.9042</v>
       </c>
       <c r="E22" t="n">
-        <v>1.1929</v>
+        <v>-1.0383</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.2286</v>
+        <v>-1.866</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.4878</v>
+        <v>-3.2041</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.735</v>
+        <v>-0.1392</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.7528</v>
+        <v>-3.0649</v>
       </c>
       <c r="J22" t="n">
-        <v>1.8328</v>
+        <v>-0.8735000000000001</v>
       </c>
       <c r="K22" t="n">
-        <v>1.2106</v>
+        <v>1.4487</v>
       </c>
       <c r="L22" t="n">
-        <v>0.6222</v>
+        <v>-2.3222</v>
       </c>
       <c r="M22" t="n">
-        <v>-3.3205</v>
+        <v>-2.3305</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.9456</v>
+        <v>-1.5879</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.375</v>
+        <v>-0.7426</v>
       </c>
       <c r="P22" t="n">
-        <v>0.6959</v>
+        <v>1.1598</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.8556</v>
+        <v>1.1598</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4551</v>
+        <v>-0.8599</v>
       </c>
       <c r="T22" t="n">
-        <v>0.2363</v>
+        <v>-0.1647</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.6915</v>
+        <v>-0.6952</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.7886</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>0.2836</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.8105</v>
+        <v>-3.373</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.789</v>
+        <v>-1.5531</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.0215</v>
+        <v>-1.8199</v>
       </c>
       <c r="G23" t="n">
         <v>-0.5562</v>
@@ -2248,13 +2248,13 @@
         <v>0.232</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.1668</v>
+        <v>-0.7292</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6721</v>
+        <v>-0.4362</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.4946</v>
+        <v>-0.293</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-7.2497</v>
+        <v>-6.71</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.2824</v>
+        <v>-4.5747</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.9672</v>
+        <v>-2.1353</v>
       </c>
       <c r="G24" t="n">
         <v>-4.9362</v>
@@ -2326,13 +2326,13 @@
         <v>1.1598</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.2955</v>
+        <v>-0.7558</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.8883</v>
+        <v>-0.1806</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.4072</v>
+        <v>-0.5753</v>
       </c>
       <c r="V24" t="n">
         <v>0.1418</v>
@@ -2362,10 +2362,10 @@
         <v>-15.9634</v>
       </c>
       <c r="E25" t="n">
-        <v>1.189100000000001</v>
+        <v>1.1892</v>
       </c>
       <c r="F25" t="n">
-        <v>-17.1524</v>
+        <v>-17.1526</v>
       </c>
       <c r="G25" t="n">
         <v>-14.6682</v>
@@ -2392,7 +2392,7 @@
         <v>-11.5161</v>
       </c>
       <c r="O25" t="n">
-        <v>-8.463900000000001</v>
+        <v>-8.463899999999999</v>
       </c>
       <c r="P25" t="n">
         <v>3.4794</v>
@@ -2404,13 +2404,13 @@
         <v>11.5978</v>
       </c>
       <c r="S25" t="n">
-        <v>-6.919</v>
+        <v>-6.9189</v>
       </c>
       <c r="T25" t="n">
-        <v>-3.0048</v>
+        <v>-3.0047</v>
       </c>
       <c r="U25" t="n">
-        <v>-3.914</v>
+        <v>-3.9141</v>
       </c>
       <c r="V25" t="n">
         <v>2.1444</v>
